--- a/Result/profitability/2433.xlsx
+++ b/Result/profitability/2433.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7575000000000001</v>
+        <v>0.64625</v>
       </c>
       <c r="N2" t="n">
-        <v>36.72125</v>
+        <v>36.89375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6775</v>
+        <v>0.6637500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>37.67874999999999</v>
+        <v>37.74375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.91</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7075</v>
+        <v>0.7137500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>38.6425</v>
+        <v>38.86875000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6887500000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>39.455</v>
+        <v>39.4075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.66875</v>
+        <v>0.57625</v>
       </c>
       <c r="N6" t="n">
-        <v>40.34375</v>
+        <v>40.47625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5287499999999999</v>
+        <v>0.51875</v>
       </c>
       <c r="N7" t="n">
-        <v>40.94625</v>
+        <v>40.91625000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.76</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5437500000000001</v>
+        <v>0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>45.2325</v>
+        <v>45.4375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2433</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>689</v>
+      </c>
+      <c r="D75" t="n">
+        <v>437</v>
+      </c>
+      <c r="E75" t="n">
+        <v>252</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>101</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.71%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>107</v>
+      </c>
+      <c r="K75" t="n">
+        <v>81</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7787500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.79625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.09803921568627461</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.640000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04701834862385312</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.02999999999999992</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.05084745762711851</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.3799999999999955</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01029810298102973</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
